--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E826"/>
+  <dimension ref="A1:E829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17778,6 +17778,69 @@
         <v>164.43</v>
       </c>
       <c r="E826" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>171.14</v>
+      </c>
+      <c r="C827" t="n">
+        <v>434.06</v>
+      </c>
+      <c r="D827" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>170.45</v>
+      </c>
+      <c r="C828" t="n">
+        <v>433.67</v>
+      </c>
+      <c r="D828" t="n">
+        <v>164.46</v>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:57+00:00</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="C829" t="n">
+        <v>434.14</v>
+      </c>
+      <c r="D829" t="n">
+        <v>164.09</v>
+      </c>
+      <c r="E829" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17794,7 +17857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B886"/>
+  <dimension ref="A1:B889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26657,6 +26720,36 @@
       </c>
       <c r="B886" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B887" t="n">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -26819,28 +26912,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2124953389381455</v>
+        <v>-0.2162469338874156</v>
       </c>
       <c r="J2" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="K2" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03511631556143102</v>
+        <v>0.0365532325982596</v>
       </c>
       <c r="M2" t="n">
-        <v>7.438109120592554</v>
+        <v>7.43061460113162</v>
       </c>
       <c r="N2" t="n">
-        <v>71.95269943848143</v>
+        <v>71.79446831422192</v>
       </c>
       <c r="O2" t="n">
-        <v>8.482493704004821</v>
+        <v>8.473161648063957</v>
       </c>
       <c r="P2" t="n">
-        <v>181.6190445965025</v>
+        <v>181.6583076949666</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26891,28 +26984,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06611205705368886</v>
+        <v>-0.0670626192179169</v>
       </c>
       <c r="J3" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="K3" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02924688234867878</v>
+        <v>0.03027984104420778</v>
       </c>
       <c r="M3" t="n">
-        <v>2.19608400943854</v>
+        <v>2.192715204775325</v>
       </c>
       <c r="N3" t="n">
-        <v>8.413424698016826</v>
+        <v>8.389633489031555</v>
       </c>
       <c r="O3" t="n">
-        <v>2.900590405075633</v>
+        <v>2.896486404081945</v>
       </c>
       <c r="P3" t="n">
-        <v>437.0870271724618</v>
+        <v>437.096974841382</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26963,28 +27056,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2344016271994871</v>
+        <v>-0.235609017372336</v>
       </c>
       <c r="J4" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="K4" t="n">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09319123763279613</v>
+        <v>0.09471910708130882</v>
       </c>
       <c r="M4" t="n">
-        <v>4.772773090720303</v>
+        <v>4.762553527767074</v>
       </c>
       <c r="N4" t="n">
-        <v>31.0058847563579</v>
+        <v>30.90428553269968</v>
       </c>
       <c r="O4" t="n">
-        <v>5.568292804474088</v>
+        <v>5.559162304943046</v>
       </c>
       <c r="P4" t="n">
-        <v>172.1790673210377</v>
+        <v>172.1917031978483</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27022,7 +27115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E826"/>
+  <dimension ref="A1:E829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49327,6 +49420,87 @@
         </is>
       </c>
     </row>
+    <row r="827">
+      <c r="A827" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>-39.33602345509087,176.93765816482036</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>-39.33660862109292,176.93578675042016</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>-39.33601729757176,176.93765714069926</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>-39.33661177603754,176.9357918099611</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:57+00:00</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>-39.336014174192485,176.9376566212176</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>-39.33660969152059,176.9357884670501</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E829"/>
+  <dimension ref="A1:E834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17841,6 +17841,111 @@
         <v>164.09</v>
       </c>
       <c r="E829" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>169.75</v>
+      </c>
+      <c r="C830" t="n">
+        <v>434.29</v>
+      </c>
+      <c r="D830" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="C831" t="n">
+        <v>434.03</v>
+      </c>
+      <c r="D831" t="n">
+        <v>164.02</v>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>169.05</v>
+      </c>
+      <c r="C832" t="n">
+        <v>434.01</v>
+      </c>
+      <c r="D832" t="n">
+        <v>164.39</v>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>168.27</v>
+      </c>
+      <c r="C833" t="n">
+        <v>433.88</v>
+      </c>
+      <c r="D833" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>166.49</v>
+      </c>
+      <c r="C834" t="n">
+        <v>433.25</v>
+      </c>
+      <c r="D834" t="n">
+        <v>164.23</v>
+      </c>
+      <c r="E834" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17857,7 +17962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B889"/>
+  <dimension ref="A1:B894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26750,6 +26855,56 @@
       </c>
       <c r="B889" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -26912,28 +27067,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2162469338874156</v>
+        <v>-0.2246278288620946</v>
       </c>
       <c r="J2" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="K2" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0365532325982596</v>
+        <v>0.03966084003800396</v>
       </c>
       <c r="M2" t="n">
-        <v>7.43061460113162</v>
+        <v>7.429202237681081</v>
       </c>
       <c r="N2" t="n">
-        <v>71.79446831422192</v>
+        <v>71.68091084997143</v>
       </c>
       <c r="O2" t="n">
-        <v>8.473161648063957</v>
+        <v>8.46645798725603</v>
       </c>
       <c r="P2" t="n">
-        <v>181.6583076949666</v>
+        <v>181.7462239275527</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26984,28 +27139,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0670626192179169</v>
+        <v>-0.0686779828985144</v>
       </c>
       <c r="J3" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="K3" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03027984104420778</v>
+        <v>0.03207212877349219</v>
       </c>
       <c r="M3" t="n">
-        <v>2.192715204775325</v>
+        <v>2.187373616019803</v>
       </c>
       <c r="N3" t="n">
-        <v>8.389633489031555</v>
+        <v>8.351489459638268</v>
       </c>
       <c r="O3" t="n">
-        <v>2.896486404081945</v>
+        <v>2.88989436824917</v>
       </c>
       <c r="P3" t="n">
-        <v>437.096974841382</v>
+        <v>437.1139220343579</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27056,28 +27211,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.235609017372336</v>
+        <v>-0.2377196485434854</v>
       </c>
       <c r="J4" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="K4" t="n">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09471910708130882</v>
+        <v>0.09735609742893792</v>
       </c>
       <c r="M4" t="n">
-        <v>4.762553527767074</v>
+        <v>4.746313760263333</v>
       </c>
       <c r="N4" t="n">
-        <v>30.90428553269968</v>
+        <v>30.73952282101986</v>
       </c>
       <c r="O4" t="n">
-        <v>5.559162304943046</v>
+        <v>5.544323477307206</v>
       </c>
       <c r="P4" t="n">
-        <v>172.1917031978483</v>
+        <v>172.2138356738369</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27115,7 +27270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E829"/>
+  <dimension ref="A1:E834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49501,6 +49656,141 @@
         </is>
       </c>
     </row>
+    <row r="830">
+      <c r="A830" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>-39.336011050813205,176.93765610173602</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>-39.336604677411806,176.9357804259946</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>-39.33600721351866,176.93765546351588</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>-39.3366092971525,176.93578783460745</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>-39.336004804054625,176.93765506277305</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>-39.33661138166948,176.93579117751847</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>-39.33599784338078,176.9376539050717</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>-39.33661031124186,176.93578946088846</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>-39.33598195876598,176.93765126313897</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>-39.33661048025675,176.9357897319353</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E834"/>
+  <dimension ref="A1:E837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17948,6 +17948,69 @@
       <c r="E834" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>166.52</v>
+      </c>
+      <c r="C835" t="n">
+        <v>433.13</v>
+      </c>
+      <c r="D835" t="n">
+        <v>164.41</v>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>165.66</v>
+      </c>
+      <c r="C836" t="n">
+        <v>433.77</v>
+      </c>
+      <c r="D836" t="n">
+        <v>163.99</v>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>164.58</v>
+      </c>
+      <c r="C837" t="n">
+        <v>434.11</v>
+      </c>
+      <c r="D837" t="n">
+        <v>163.84</v>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17962,7 +18025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B894"/>
+  <dimension ref="A1:B897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26905,6 +26968,36 @@
       </c>
       <c r="B894" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -27067,28 +27160,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2246278288620946</v>
+        <v>-0.2315879561234851</v>
       </c>
       <c r="J2" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="K2" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03966084003800396</v>
+        <v>0.04216540241848099</v>
       </c>
       <c r="M2" t="n">
-        <v>7.429202237681081</v>
+        <v>7.438201710392587</v>
       </c>
       <c r="N2" t="n">
-        <v>71.68091084997143</v>
+        <v>71.78642504691409</v>
       </c>
       <c r="O2" t="n">
-        <v>8.46645798725603</v>
+        <v>8.472687002770378</v>
       </c>
       <c r="P2" t="n">
-        <v>181.7462239275527</v>
+        <v>181.8194875192648</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27139,28 +27232,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0686779828985144</v>
+        <v>-0.06977194054599729</v>
       </c>
       <c r="J3" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="K3" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03207212877349219</v>
+        <v>0.03328413401441754</v>
       </c>
       <c r="M3" t="n">
-        <v>2.187373616019803</v>
+        <v>2.184852073287528</v>
       </c>
       <c r="N3" t="n">
-        <v>8.351489459638268</v>
+        <v>8.331041624643678</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88989436824917</v>
+        <v>2.88635438306589</v>
       </c>
       <c r="P3" t="n">
-        <v>437.1139220343579</v>
+        <v>437.1254330704038</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27211,28 +27304,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2377196485434854</v>
+        <v>-0.2388953027481215</v>
       </c>
       <c r="J4" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="K4" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09735609742893792</v>
+        <v>0.09889661587775589</v>
       </c>
       <c r="M4" t="n">
-        <v>4.746313760263333</v>
+        <v>4.736119125927841</v>
       </c>
       <c r="N4" t="n">
-        <v>30.73952282101986</v>
+        <v>30.63970127928547</v>
       </c>
       <c r="O4" t="n">
-        <v>5.544323477307206</v>
+        <v>5.535314018128102</v>
       </c>
       <c r="P4" t="n">
-        <v>172.2138356738369</v>
+        <v>172.2262114698063</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27270,7 +27363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E834"/>
+  <dimension ref="A1:E837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49791,6 +49884,87 @@
         </is>
       </c>
     </row>
+    <row r="835">
+      <c r="A835" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>-39.335982226484184,176.93765130766593</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>-39.33661149434607,176.93579135821636</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>-39.33597455189496,176.93765003122704</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>-39.33660912813762,176.93578756356064</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>-39.33596491403866,176.93764842825777</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>-39.33660828306313,176.9357862083265</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
